--- a/config/GPIO.xlsx
+++ b/config/GPIO.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="22010" windowHeight="12332"/>
   </bookViews>
   <sheets>
     <sheet name="gpio" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
   <si>
     <t>id</t>
   </si>
@@ -62,85 +62,115 @@
     <t>DO</t>
   </si>
   <si>
-    <t>gpiochip2</t>
+    <t>/dev/gpiochip2</t>
+  </si>
+  <si>
+    <t>运行指示灯</t>
+  </si>
+  <si>
+    <t>{"en":"Run Indicator"}</t>
+  </si>
+  <si>
+    <t>DO1</t>
+  </si>
+  <si>
+    <t>告警指示灯</t>
+  </si>
+  <si>
+    <t>{"en":"Alarm Indicator"}</t>
+  </si>
+  <si>
+    <t>DO2</t>
+  </si>
+  <si>
+    <t>故障跳闸</t>
+  </si>
+  <si>
+    <t>{"en":"Fault Trip"}</t>
+  </si>
+  <si>
+    <t>DO3</t>
+  </si>
+  <si>
+    <t>消防报警</t>
+  </si>
+  <si>
+    <t>{"en":"Fire Alarm"}</t>
+  </si>
+  <si>
+    <t>DO4</t>
+  </si>
+  <si>
+    <t>DO5</t>
+  </si>
+  <si>
+    <t>DO6</t>
+  </si>
+  <si>
+    <t>DO7</t>
+  </si>
+  <si>
+    <t>DIN0</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>/dev/gpiochip3</t>
   </si>
   <si>
     <t>门禁</t>
   </si>
   <si>
-    <t>DO1</t>
+    <t>{"en":"Access Control"}</t>
+  </si>
+  <si>
+    <t>DIN1</t>
   </si>
   <si>
     <t>浪涌</t>
   </si>
   <si>
-    <t>DO2</t>
-  </si>
-  <si>
-    <t>DO3</t>
+    <t>{"en":"Surge Protection"}</t>
+  </si>
+  <si>
+    <t>DIN2</t>
+  </si>
+  <si>
+    <t>DIN3</t>
   </si>
   <si>
     <t>消防</t>
   </si>
   <si>
-    <t>DO4</t>
+    <t>{"en":"Fire Protection"}</t>
+  </si>
+  <si>
+    <t>DIN4</t>
   </si>
   <si>
     <t>水侵</t>
   </si>
   <si>
-    <t>DO5</t>
+    <t>{"en":"Water Intrusion"}</t>
+  </si>
+  <si>
+    <t>DIN5</t>
   </si>
   <si>
     <t>急停</t>
   </si>
   <si>
-    <t>DO6</t>
+    <t>{"en":"Emergency Stop"}</t>
+  </si>
+  <si>
+    <t>DIN6</t>
   </si>
   <si>
     <t>QF断路器</t>
   </si>
   <si>
-    <t>DO7</t>
-  </si>
-  <si>
-    <t>DIN0</t>
-  </si>
-  <si>
-    <t>DI</t>
-  </si>
-  <si>
-    <t>gpiochip3</t>
-  </si>
-  <si>
-    <t>运行指示灯</t>
-  </si>
-  <si>
-    <t>DIN1</t>
-  </si>
-  <si>
-    <t>告警指示灯</t>
-  </si>
-  <si>
-    <t>DIN2</t>
-  </si>
-  <si>
-    <t>故障跳闸</t>
-  </si>
-  <si>
-    <t>DIN3</t>
-  </si>
-  <si>
-    <t>消防报警</t>
-  </si>
-  <si>
-    <t>DIN4</t>
-  </si>
-  <si>
-    <t>DIN5</t>
-  </si>
-  <si>
-    <t>DIN6</t>
+    <t>{"en":"Circuit Breaker (QF)"}</t>
   </si>
   <si>
     <t>DIN7</t>
@@ -767,7 +797,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -779,6 +809,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1305,16 +1338,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="3" width="9.11111111111111" style="2"/>
-    <col min="4" max="5" width="17.5982905982906" style="2" customWidth="1"/>
+    <col min="4" max="5" width="17.5952380952381" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.11111111111111" style="2"/>
-    <col min="7" max="7" width="20.7435897435897" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.7460317460317" style="2" customWidth="1"/>
     <col min="8" max="8" width="9.11111111111111" style="2"/>
-    <col min="9" max="9" width="20.008547008547" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.11111111111111" style="2"/>
+    <col min="9" max="9" width="31.3492063492063" style="2" customWidth="1"/>
+    <col min="10" max="10" width="25.4444444444444" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.11111111111111" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:9">
@@ -1368,13 +1402,19 @@
       <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
         <v>89</v>
@@ -1389,7 +1429,13 @@
         <v>25</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1397,7 +1443,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2">
         <v>90</v>
@@ -1411,8 +1457,14 @@
       <c r="F4" s="2">
         <v>26</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1420,7 +1472,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2">
         <v>91</v>
@@ -1435,7 +1487,13 @@
         <v>27</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1443,7 +1501,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2">
         <v>92</v>
@@ -1457,8 +1515,8 @@
       <c r="F6" s="2">
         <v>28</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>19</v>
+      <c r="H6" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1466,7 +1524,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C7" s="2">
         <v>93</v>
@@ -1480,8 +1538,8 @@
       <c r="F7" s="2">
         <v>29</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>21</v>
+      <c r="H7" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1489,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2">
         <v>94</v>
@@ -1503,8 +1561,8 @@
       <c r="F8" s="2">
         <v>30</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>23</v>
+      <c r="H8" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1512,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2">
         <v>95</v>
@@ -1535,22 +1593,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2">
         <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1558,22 +1622,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C11" s="2">
         <v>97</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1581,22 +1651,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C12" s="2">
         <v>98</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F12" s="2">
         <v>2</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>32</v>
+      <c r="H12" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1604,22 +1674,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C13" s="2">
         <v>99</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F13" s="2">
         <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1627,22 +1703,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2">
         <v>100</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
       </c>
+      <c r="G14" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="H14" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1650,22 +1732,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2">
         <v>101</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F15" s="2">
         <v>5</v>
       </c>
+      <c r="G15" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="H15" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1673,22 +1761,28 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2">
         <v>102</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F16" s="2">
         <v>6</v>
       </c>
+      <c r="G16" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="H16" s="2">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1696,16 +1790,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2">
         <v>103</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="F17" s="2">
         <v>7</v>
@@ -1713,6 +1807,9 @@
       <c r="H17" s="2">
         <v>0</v>
       </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="E18" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
